--- a/Figure 2/Figure 2-G.xlsx
+++ b/Figure 2/Figure 2-G.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6D6A8F-8C57-40EE-A4FE-C1B168BA5803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D35C33-D284-43A8-887B-3206552C6C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24580" yWindow="1850" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +158,12 @@
       <name val="等线"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -179,16 +185,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,18 +482,19 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.58203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.58203125" style="2" customWidth="1"/>
     <col min="2" max="4" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -492,13 +502,13 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>278.48486666666662</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>236.85177321428569</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>1.175776997095624</v>
       </c>
     </row>
@@ -506,13 +516,13 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>283.67457551020391</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>232.11378979591822</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>1.2221358143332179</v>
       </c>
     </row>
@@ -520,13 +530,13 @@
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>309.92368686868662</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>255.99184090909068</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="4">
         <v>1.2106779878923895</v>
       </c>
     </row>
@@ -534,13 +544,13 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>253.63964285714269</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>200.81549809523781</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="4">
         <v>1.263048147493341</v>
       </c>
     </row>
@@ -548,13 +558,13 @@
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>283.35750736434079</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>261.27231279069736</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="4">
         <v>1.0845294104750229</v>
       </c>
     </row>
@@ -562,13 +572,13 @@
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>261.09867510040135</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>252.92550682730894</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="4">
         <v>1.0323145276078178</v>
       </c>
     </row>
@@ -576,13 +586,13 @@
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>246.24589351851827</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>284.62572037037017</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="4">
         <v>0.86515685651349428</v>
       </c>
     </row>
@@ -590,13 +600,13 @@
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>239.10055925925903</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>228.48513641975282</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="4">
         <v>1.0464600148869398</v>
       </c>
     </row>
@@ -604,13 +614,13 @@
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>219.01715866666635</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>278.20060311111081</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="4">
         <v>0.78726342149298978</v>
       </c>
     </row>
@@ -618,13 +628,13 @@
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="4">
         <v>263.38395333333312</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="4">
         <v>314.92554962962936</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="4">
         <v>0.83633720300905356</v>
       </c>
     </row>
@@ -632,13 +642,13 @@
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="4">
         <v>275.98927511111083</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="4">
         <v>261.70482444444417</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="4">
         <v>1.0545822978120107</v>
       </c>
     </row>
@@ -646,13 +656,13 @@
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="4">
         <v>272.35381811594192</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="4">
         <v>248.81162101449252</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="4">
         <v>1.0946185592355355</v>
       </c>
     </row>
@@ -660,13 +670,13 @@
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="4">
         <v>224.6670641025639</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="4">
         <v>209.43075512820485</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="4">
         <v>1.0727510578139872</v>
       </c>
     </row>
@@ -674,13 +684,13 @@
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="4">
         <v>269.94083666666637</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="4">
         <v>284.86716222222202</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="4">
         <v>0.94760250553585468</v>
       </c>
     </row>
@@ -688,13 +698,13 @@
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>222.63219429824537</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>295.86565175438568</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="4">
         <v>0.75247732536071665</v>
       </c>
     </row>
@@ -702,13 +712,13 @@
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>314.21114727891137</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>290.92619141914162</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="4">
         <v>1.0800373309332703</v>
       </c>
     </row>
@@ -716,13 +726,13 @@
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="4">
         <v>299.38893585858557</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="4">
         <v>246.30761313131276</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="4">
         <v>1.2155082502422441</v>
       </c>
     </row>
@@ -730,13 +740,13 @@
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>282.6466804347823</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>188.62351050724615</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="4">
         <v>1.4984700458319811</v>
       </c>
     </row>
@@ -744,13 +754,13 @@
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="4">
         <v>271.23312988505717</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="4">
         <v>236.91926436781586</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="4">
         <v>1.1448335812151149</v>
       </c>
     </row>
@@ -758,13 +768,13 @@
       <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="4">
         <v>263.4142164609051</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="4">
         <v>275.5010391666666</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="4">
         <v>0.95612785076121098</v>
       </c>
     </row>
@@ -772,13 +782,13 @@
       <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>279.88190041666638</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <v>242.69337166666648</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="4">
         <v>1.1532325687125786</v>
       </c>
     </row>
